--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
@@ -724,12 +724,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>調整交付金見込交付割合の算定。第9期からの逆算値5.963％の更新</t>
+          <t>調整交付金見込交付割合の算定。第9期からの逆算値6.148％の更新</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>**1ptで月額290円規模**</t>
+          <t>**1ptで月額281円規模**</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1％で月額3.7円。3年計で約207,000千円の規模</t>
+          <t>1％で月額4.2円。3年計で約207,000千円の規模</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1％で月額62円。±1.5％を感度分析に併記済み</t>
+          <t>1％で月額61円。±1.5％を感度分析に併記済み</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>5.96261318317115</v>
+        <v>6.148121147818893</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>6569.308187605308</v>
+        <v>6570.072467646066</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>6466.57441855681</v>
+        <v>6467.338698597566</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>6269.668027880518</v>
+        <v>6270.432307921275</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>-290.234938252619</v>
+        <v>-281.3533350127354</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>-85.61147420708312</v>
+        <v>-85.61147420708403</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>62.00292275880383</v>
+        <v>61.48098991355346</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>限界率22.04％＝23％＋5％－5.963％</t>
+          <t>限界率21.85％＝23％＋5％－6.148％</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>3.690159117247276</v>
+        <v>4.219734762906228</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>62.00292275880383</v>
+        <v>61.48098991355346</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>**1ptで月額281円規模**</t>
+          <t>**1ptで月額269円規模**</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1％で月額4.2円。3年計で約207,000千円の規模</t>
+          <t>1％で月額4.0円。3年計で約207,000千円の規模</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>**1,000万円で月額86円**</t>
+          <t>**1,000万円で月額82円**</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>第9期の補正係数は0.968だが、令和7年度実績では0.952。低所得段階の割合が上がっている</t>
+          <t>第9期の補正係数は0.974（補正後10,136人÷第1号10,409人）、令和7年度末の構成では0.996。**いずれも軽減前の標準割合による**</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>分母。補正係数0.016の差は月額約110円</t>
+          <t>分母。補正係数0.02の差は月額約130円</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>**1ptで月額298円**</t>
+          <t>**1ptで月額285円**</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1％で月額61円。±1.5％を感度分析に併記済み</t>
+          <t>1％で月額59円。±1.5％を感度分析に併記済み</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.9526088478366556</v>
+        <v>0.9960831307729705</v>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>令和7年度末の所得段階別構成による。第9期の算定では0.968</t>
+          <t>**令和7年度末の所得段階別構成に、軽減前の標準割合（0.455／0.685／0.690ほか）を当てたもの。第9期の算定では0.974**</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>9797.582000000002</v>
+        <v>10244.715</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>6570.072467646066</v>
+        <v>6283.320106777462</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>6467.338698597566</v>
+        <v>6185.070177284867</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>6270.432307921275</v>
+        <v>5996.757812424058</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>297.7692245819198</v>
+        <v>284.773016615668</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>-281.3533350127354</v>
+        <v>-269.0736024145845</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>-85.61147420708403</v>
+        <v>-81.87494124382829</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>61.48098991355346</v>
+        <v>58.79763762283346</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>4.219734762906228</v>
+        <v>4.035563444937907</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>61.48098991355346</v>
+        <v>58.79763762283346</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>**1ptで月額269円規模**</t>
+          <t>**1ptで月額278円規模**</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1％で月額4.0円。3年計で約207,000千円の規模</t>
+          <t>1％で月額3.5円。3年計で約207,000千円の規模</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>6283.320106777462</v>
+        <v>6231.098189700424</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>6185.070177284867</v>
+        <v>6132.848260207828</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5996.757812424058</v>
+        <v>5944.53589534702</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>284.773016615668</v>
+        <v>284.7730166156662</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>-269.0736024145845</v>
+        <v>-277.5675659884118</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>-81.87494124382829</v>
+        <v>-81.87494124383011</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>4.035563444937907</v>
+        <v>3.513344274168048</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>令和8年度が何か月分かの確定。川崎町では令和8年5月の1か月だった</t>
+          <t>令和8年度が何か月分かの確定。他町村の案件①では令和8年5月の1か月だった</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>推計の中身を追えるようにする。金ケ崎町は受領済み</t>
+          <t>推計の中身を追えるようにする。他町村の案件でも同じ様式を受け取っている</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>利用者負担の見直し・特定入所者介護サービス費の制度改正の財政影響。金ケ崎町の第10期ワークシートではいずれも1（影響なし）のまま</t>
+          <t>利用者負担の見直し・特定入所者介護サービス費の制度改正の財政影響。他町村の案件でも第10期ワークシートはいずれも1（影響なし）のまま</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>年報は令和3〜7年度がいずれも12か月。国保連月報は令和8年7月審査分まで。**川崎町・金ケ崎町では見える化の令和8年度が1か月ないし公表時点データであったが、小野町は年報を直接使っているためこの問題は生じていない**</t>
+          <t>年報は令和3〜7年度がいずれも12か月。国保連月報は令和8年7月審査分まで。**他町村の案件2件では見える化の令和8年度が1か月ないし公表時点データであったが、小野町は年報を直接使っているためこの問題は生じていない**</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>※ 保険料の算式（金ケ崎町の第10期で確立した5式）</t>
+          <t>※ 保険料の算式（他町村の案件②の第10期で確立した5式）</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
@@ -983,12 +983,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の残高と取崩実績（**依頼票S3**）</t>
+          <t>介護給付費準備基金の令和7年度末の残高（**依頼票S3**）</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>令和4年度末120,000千円が令和5・6年度末に12,000千円へ1桁減っている</t>
+          <t>令和5年度末120,000千円は町の財務書類で確認済み。年報 様式4 の保有額は財務書類と合わない</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1868,7 +1868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2151,11 +2151,11 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　準備基金12,000千円を全額取崩</t>
+          <t xml:space="preserve">　準備基金105,000千円を取崩</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>6132.848260207828</v>
+        <v>5371.411306640209</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>保有額の全額</t>
+          <t>令和8年度末見込の半分</t>
         </is>
       </c>
     </row>
@@ -2176,11 +2176,11 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">　第9期と同じ35,000千円を取崩</t>
+          <t xml:space="preserve">　準備基金210,000千円を全額取崩</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>5944.53589534702</v>
+        <v>4511.724423579994</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>**保有額12,000千円では実行できない**</t>
+          <t>令和8年度末見込の全額</t>
         </is>
       </c>
     </row>
@@ -2201,11 +2201,11 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>第9期の保険料基準額（月額）</t>
+          <t xml:space="preserve">　第9期と同じ35,000千円を取崩</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>6600</v>
+        <v>5944.53589534702</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>第9期計画本文</t>
+          <t>残高の範囲内で実行できる</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>感応度</t>
+          <t>結果</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>第1号被保険者負担割合 1pt</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>284.7730166156662</v>
+          <t>第9期の保険料基準額（月額）</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>6600</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>円/月</t>
+          <t>円</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>**政令。23→24％で上昇**</t>
+          <t>第9期計画本文</t>
         </is>
       </c>
     </row>
@@ -2251,11 +2251,11 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>調整交付金見込交付割合 1pt</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>-277.5675659884118</v>
+          <t>第1号被保険者負担割合 1pt</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>284.7730166156662</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>**割合が上がると保険料は下がる**</t>
+          <t>**政令。23→24％で上昇**</t>
         </is>
       </c>
     </row>
@@ -2276,18 +2276,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>準備基金の取崩 1,000万円</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>-81.87494124383011</v>
+          <t>調整交付金見込交付割合 1pt</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>-277.5675659884118</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>円/月</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>**割合が上がると保険料は下がる**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2297,22 +2301,18 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>総給付費 1％</t>
+          <t>準備基金の取崩 1,000万円</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>58.79763762283346</v>
+        <v>-81.87494124383011</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>円/月</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>限界率21.85％＝23％＋5％－6.148％</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2322,18 +2322,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>地域支援事業費 1％</t>
+          <t>総給付費 1％</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>3.513344274168048</v>
+        <v>58.79763762283346</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>円/月</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>限界率21.85％＝23％＋5％－6.148％</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2343,74 +2347,95 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>地域支援事業費 1％</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>3.513344274168048</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>円/月</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>感応度</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>介護報酬改定 1％</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C21" s="12" t="n">
         <v>58.79763762283346</v>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>円/月</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>令和9年度改定</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>※ 保険料の算式（他町村の案件②の第10期で確立した5式）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 ①標準給付費＝総給付費＋特定入所者＋高額介護＋高額医療合算＋審査支払手数料</t>
+          <t>※ 保険料の算式（他町村の案件②の第10期で確立した5式）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 ②第1号負担分相当額＝（①＋地域支援事業費）×第1号負担割合</t>
+          <t xml:space="preserve">　 ①標準給付費＝総給付費＋特定入所者＋高額介護＋高額医療合算＋審査支払手数料</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 ③調整交付金相当額＝（①＋総合事業費）×5％　**包括的支援事業・任意事業費は対象外**</t>
+          <t xml:space="preserve">　 ②第1号負担分相当額＝（①＋地域支援事業費）×第1号負担割合</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 ④保険料収納必要額＝②＋③－調整交付金見込額－準備基金取崩額</t>
+          <t xml:space="preserve">　 ③調整交付金相当額＝（①＋総合事業費）×5％　**包括的支援事業・任意事業費は対象外**</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 ⑤保険料基準額＝④÷予定収納率÷補正後被保険者数÷12</t>
+          <t xml:space="preserve">　 ④保険料収納必要額＝②＋③－調整交付金見込額－準備基金取崩額</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>※ 見込交付割合＝（α＋0.05）－α×後期高齢者加入割合補正係数×所得段階別加入割合補正係数。**第10期の全国値は見える化の係数シートで確認する（Ａ4）**</t>
+          <t xml:space="preserve">　 ⑤保険料基準額＝④÷予定収納率÷補正後被保険者数÷12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>※ 見込交付割合＝（α＋0.05）－α×後期高齢者加入割合補正係数×所得段階別加入割合補正係数。**第10期の全国値は見える化の係数シートで確認する（Ａ4）**</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>**※ 地域支援事業費・調整交付金・準備基金・第1号負担割合のいずれもが未確定です。上の保険料基準額は確定値ではありません。**</t>
         </is>

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260915.xlsx
@@ -724,12 +724,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>調整交付金見込交付割合の算定。第9期からの逆算値6.148％の更新</t>
+          <t>調整交付金見込交付割合の算定。現在の5.533％は受領ワークシートの係数による</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>**1ptで月額278円規模**</t>
+          <t>**1ptで月額262円規模**</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1％で月額3.5円。3年計で約207,000千円の規模</t>
+          <t>1％で月額3.6円。3年計で約207,000千円の規模</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>**1ptで月額285円**</t>
+          <t>**1ptで月額269円**</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1％で月額59円。±1.5％を感度分析に併記済み</t>
+          <t>1％で月額57円。±1.5％を感度分析に併記済み</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>3286397.502420967</v>
+        <v>3093948.167011783</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>191748.708</v>
+        <v>194662.125</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>**年報 様式4 の令和6年度決算（63,916千円）を3年度とも据え置いた。事業別の内訳は様式4になく未受領（依頼票S6）**</t>
+          <t>**令和7年度の実績を3年度とも据え置いた（素案と同じ）**</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>103743.141</v>
+        <v>103719.444</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>10285</v>
+        <v>10284</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.9960831307729705</v>
+        <v>0.9961799883313888</v>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>6.148121147818893</v>
+        <v>5.533219116080939</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>**第9期計画の公表値から逆算した小野町の実績値**</t>
+          <t>**算式（後期高齢者加入割合補正係数×所得段階別加入割合補正係数）による。第10期3年の平均**</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>6231.098189700424</v>
+        <v>6053.258329553852</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>5371.411306640209</v>
+        <v>5193.571446493636</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4511.724423579994</v>
+        <v>4333.884563433421</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>5944.53589534702</v>
+        <v>5766.696035200446</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>284.7730166156662</v>
+        <v>269.2547744323183</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>-277.5675659884118</v>
+        <v>-261.8088477688889</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>58.79763762283346</v>
+        <v>56.91213587680249</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>限界率21.85％＝23％＋5％－6.148％</t>
+          <t>限界率22.47％＝23％＋5％－5.533％</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>3.513344274168048</v>
+        <v>3.620447418736148</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>58.79763762283346</v>
+        <v>56.91213587680249</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 ④保険料収納必要額＝②＋③－調整交付金見込額－準備基金取崩額</t>
+          <t xml:space="preserve">　 ④保険料収納必要額＝②＋③－調整交付金見込額（＝（①＋総合事業費）×見込交付割合）－準備基金取崩額</t>
         </is>
       </c>
     </row>
